--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>208.25</v>
+        <v>223.69</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>183.97</v>
+        <v>200.13</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>178.68</v>
+        <v>195.18</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>157.52</v>
+        <v>169.53</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>154.15</v>
+        <v>168.18</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>152.9</v>
+        <v>163.34</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>149.85</v>
+        <v>161.71</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>146.7</v>
+        <v>157.91</v>
       </c>
     </row>
     <row r="10">
@@ -677,7 +677,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>144.74</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>135.53</v>
+        <v>147.16</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +711,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>133.83</v>
+        <v>145.97</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>131.78</v>
+        <v>142.47</v>
       </c>
     </row>
     <row r="14">
@@ -745,7 +745,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>130.38</v>
+        <v>140.99</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>129.4</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>128.49</v>
+        <v>138.89</v>
       </c>
     </row>
     <row r="17">
@@ -796,7 +796,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>128.33</v>
+        <v>138.04</v>
       </c>
     </row>
     <row r="18">
@@ -813,7 +813,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>115.55</v>
+        <v>124.89</v>
       </c>
     </row>
     <row r="19">
@@ -830,7 +830,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>105.29</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="20">
@@ -847,7 +847,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>102.68</v>
+        <v>108.49</v>
       </c>
     </row>
     <row r="21">
@@ -864,7 +864,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>85.39</v>
+        <v>91.64</v>
       </c>
     </row>
     <row r="22">
@@ -881,7 +881,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>73.36</v>
+        <v>76.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:30</t>
+    <t xml:space="preserve">2026-10-04 10:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:43</t>
+    <t xml:space="preserve">2026-10-05 16:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
